--- a/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6801LL.xlsx
+++ b/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6801LL.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -524,37 +524,52 @@
           <t>ORB_GRVW@DRIVE</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>ORB_I3@DRIVE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>ORB_THDL@DRIVE</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>$PRP@PartNo</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>$PRP@Threads</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>$PRP@DataStatus</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>$PRP@AxialSource</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>$COMMENT</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>$PRP@ScopeAction</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -596,33 +611,39 @@
       <c r="K3" s="3" t="n">
         <v>0.075</v>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>6801-LL-04-04-NWO-FG</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>7/16-20 (JIC) x 7/16-20 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family | ORB_I3 0.73 = Air-Way 6801 rows of the -04 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_THDL 0.265 = Air-Way 6801 rows of the -04 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08)</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>6801-LL-04-04-NWO-FG</t>
         </is>
@@ -664,32 +685,32 @@
       <c r="K4" s="3" t="n">
         <v>0.075</v>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>6801-LL-04-04-NWO</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>7/16-20 (JIC) x 7/16-20 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="S4" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -731,32 +752,32 @@
       <c r="K5" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>6801-LL-04-06-NWO</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>7/16-20 (JIC) x 9/16-18 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -798,32 +819,32 @@
       <c r="K6" s="3" t="n">
         <v>0.075</v>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="O6" s="3" t="inlineStr">
         <is>
           <t>6801-LL-06-04-NWO</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>9/16-18 (JIC) x 7/16-20 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="S6" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -865,33 +886,39 @@
       <c r="K7" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>6801-LL-06-06-NWO-FG</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>9/16-18 (JIC) x 9/16-18 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family | ORB_I3 0.75 = Air-Way 6801 rows of the -06 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_THDL 0.312 = Air-Way 6801 rows of the -06 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08)</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>6801-LL-06-06-NWO-FG</t>
         </is>
@@ -933,32 +960,32 @@
       <c r="K8" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="O8" s="3" t="inlineStr">
         <is>
           <t>6801-LL-06-06-NWO</t>
         </is>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>9/16-18 (JIC) x 9/16-18 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="S8" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1000,32 +1027,32 @@
       <c r="K9" s="3" t="n">
         <v>0.094</v>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="O9" s="3" t="inlineStr">
         <is>
           <t>6801-LL-06-08-NWO</t>
         </is>
       </c>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>9/16-18 (JIC) x 3/4-16 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="S9" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1067,32 +1094,32 @@
       <c r="K10" s="3" t="n">
         <v>0.083</v>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
         <is>
           <t>6801-LL-08-06-NWO</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>3/4-16 (JIC) x 9/16-18 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1134,37 +1161,37 @@
       <c r="K11" s="4" t="n">
         <v>0.094</v>
       </c>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>6801-LL-08-08-NWO-FG</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>3/4-16 (JIC) x 7/8-14 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>ASSUMED</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
-        <is>
-          <t>B(2) printed 7/8-14 with dims duplicating the 8-10 rows (an 8-8 takes 3/4-16; non-FG 8-8 prints it) - as-printed, likely scrambled row</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>B(2) printed 7/8-14 with dims duplicating the 8-10 rows (an 8-8 takes 3/4-16; non-FG 8-8 prints it) - as-printed, likely scrambled row | HELD 2026-10-21 (group B): Air-Way prints this row with exactly the 6801-LL-08-10 values (M12 3.25, locknut 1.00, ORB bore 0.48; open question D 2026-10-18 "ignore it? recommended yes") - Brennan CAD record: M 1.25, M7 2.48, C 0.875, Y 0.75, B1D 0.391, B2D 0.391; BRENNAN_6801-LL-08-08-NWO-FG: ORB tip 2.480, JIC leg 1.250</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>6801-LL-08-08-NWO-FG</t>
         </is>
@@ -1206,32 +1233,32 @@
       <c r="K12" s="3" t="n">
         <v>0.094</v>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>6801-LL-08-08-NWO</t>
         </is>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>3/4-16 (JIC) x 3/4-16 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="R12" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="S12" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1273,32 +1300,32 @@
       <c r="K13" s="3" t="n">
         <v>0.107</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>6801-LL-08-10-NWO</t>
         </is>
       </c>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>3/4-16 (JIC) x 7/8-14 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="R13" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="S13" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1340,32 +1367,32 @@
       <c r="K14" s="3" t="n">
         <v>0.094</v>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr">
         <is>
           <t>6801-LL-10-08-NWO</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>7/8-14 (JIC) x 3/4-16 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="R14" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1407,32 +1434,32 @@
       <c r="K15" s="3" t="n">
         <v>0.107</v>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>6801-LL-10-10-NWO</t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>7/8-14 (JIC) x 7/8-14 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1474,32 +1501,32 @@
       <c r="K16" s="3" t="n">
         <v>0.094</v>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
         <is>
           <t>6801-LL-12-08-NWO</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
+      <c r="P16" s="3" t="inlineStr">
         <is>
           <t>1 1/16-12 (JIC) x 3/4-16 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N16" s="3" t="inlineStr">
+      <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="S16" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1541,32 +1568,32 @@
       <c r="K17" s="3" t="n">
         <v>0.107</v>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr">
         <is>
           <t>6801-LL-12-10-NWO</t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>1 1/16-12 (JIC) x 7/8-14 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr">
+      <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1608,32 +1635,32 @@
       <c r="K18" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="O18" s="3" t="inlineStr">
         <is>
           <t>6801-LL-12-12-NWO</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="P18" s="3" t="inlineStr">
         <is>
           <t>1 1/16-12 (JIC) x 1 1/16-12 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N18" s="3" t="inlineStr">
+      <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
+      <c r="R18" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6801-LL-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1675,32 +1702,32 @@
       <c r="K19" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="O19" s="3" t="inlineStr">
         <is>
           <t>6801-LL-12-16-NWO</t>
         </is>
       </c>
-      <c r="M19" s="3" t="inlineStr">
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>1 1/16-12 (JIC) x 1 5/16-12 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr">
+      <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
+      <c r="S19" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1742,32 +1769,32 @@
       <c r="K20" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="O20" s="3" t="inlineStr">
         <is>
           <t>6801-LL-16-12-NWO</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>1 5/16-12 (JIC) x 1 1/16-12 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N20" s="3" t="inlineStr">
+      <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
+      <c r="R20" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
+      <c r="S20" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1809,32 +1836,32 @@
       <c r="K21" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="O21" s="3" t="inlineStr">
         <is>
           <t>6801-LL-16-16-NWO</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>1 5/16-12 (JIC) x 1 5/16-12 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N21" s="3" t="inlineStr">
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="R21" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6801-LL-16-16-NWO-FG</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1876,32 +1903,32 @@
       <c r="K22" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="O22" s="3" t="inlineStr">
         <is>
           <t>6801-LL-20-20-NWO</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="P22" s="3" t="inlineStr">
         <is>
           <t>1 5/8-12 (JIC) x 1 5/8-12 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N22" s="3" t="inlineStr">
+      <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="S22" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23) | near-match donor for OMi SKU 6801-LL-20-20-NWO-FG</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1943,32 +1970,32 @@
       <c r="K23" s="3" t="n">
         <v>0.125</v>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="O23" s="3" t="inlineStr">
         <is>
           <t>6801-LL-24-24-NWO</t>
         </is>
       </c>
-      <c r="M23" s="3" t="inlineStr">
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>1 7/8-12 (JIC) x 1 7/8-12 (male ORB) long pattern</t>
         </is>
       </c>
-      <c r="N23" s="3" t="inlineStr">
+      <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="R23" s="3" t="inlineStr">
         <is>
           <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
+      <c r="S23" s="3" t="inlineStr">
         <is>
           <t>DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>DROP</t>
         </is>
@@ -1980,32 +2007,70 @@
           <t>6801-LL-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="B24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>6801-LL-12-12-NWO-FG</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-LL-12-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-LL-12-12-NWO dims are NOT assumed; confirm before modelling</t>
-        </is>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M@DRIVE, M12@DRIVE, C4HEX@HEX, Y@REF, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-LL-12-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | ORB_I3 1.14 = Air-Way 6801 rows of the -12 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_THDL 0.469 = Air-Way 6801 rows of the -12 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_GRVDIA 0.945 = Air-Way 6801 rows of the -12 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08)</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-LL-12-12-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-LL-12-12-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M@DRIVE=M, M12@DRIVE=M7, C4HEX@HEX=C, Y@REF=Y, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>6801-LL-12-12-NWO-FG</t>
         </is>
@@ -2017,32 +2082,70 @@
           <t>6801-LL-16-16-NWO-FG</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="B25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>6801-LL-16-16-NWO-FG</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-LL-16-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-LL-16-16-NWO dims are NOT assumed; confirm before modelling</t>
-        </is>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M@DRIVE, M12@DRIVE, C4HEX@HEX, Y@REF, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-LL-16-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | ORB_I3 1.14 = Air-Way 6801 rows of the -16 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_THDL 0.469 = Air-Way 6801 rows of the -16 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_GRVDIA 1.195 = Air-Way 6801 rows of the -16 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08)</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-LL-16-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-LL-16-16-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M@DRIVE=M, M12@DRIVE=M7, C4HEX@HEX=C, Y@REF=Y, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>6801-LL-16-16-NWO-FG</t>
         </is>
@@ -2054,32 +2157,70 @@
           <t>6801-LL-20-20-NWO-FG</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="B26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>6801-LL-20-20-NWO-FG</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-LL-20-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-LL-20-20-NWO dims are NOT assumed; confirm before modelling</t>
-        </is>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21 group B: M@DRIVE, M12@DRIVE, C4HEX@HEX, Y@REF, D1@BORE, D2@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6801-LL-20-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied | ORB_I3 1.14 = Air-Way 6801 rows of the -20 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_THDL 0.469 = Air-Way 6801 rows of the -20 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_GRVDIA 1.507 = Air-Way 6801 rows of the -20 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08)</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6801-LL-20-20-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6801-LL-20-20-NWO-FG (PARTcommunity / CADENAS, group B 2026-10-21: M@DRIVE=M, M12@DRIVE=M7, C4HEX@HEX=C, Y@REF=Y, D1@BORE=B1D, D2@BORE=B2D; user 2026-10-21 "yes you can use them following my rule")</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>6801-LL-20-20-NWO-FG</t>
         </is>

--- a/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6801LL.xlsx
+++ b/tools/_out/groupB_20261021/stage/04_DESIGN_TABLES/DesignTable_6801LL.xlsx
@@ -1132,22 +1132,22 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3.25</v>
+        <v>2.48</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.48</v>
+        <v>0.391</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0.75</v>
@@ -1161,6 +1161,17 @@
       <c r="K11" s="4" t="n">
         <v>0.094</v>
       </c>
+      <c r="L11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
+        </is>
+      </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
           <t>6801-LL-08-08-NWO-FG</t>
@@ -1173,17 +1184,17 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family</t>
+          <t>[BRENNAN-CELL 2026-10-21: M@DRIVE, M12@DRIVE, C4HEX@HEX, Y@REF, D1@BORE, D2@BORE] Air-Way s136 only (double-pass 21 rows); M matches verified 6801 family | ORB_I3 0.86 = Air-Way 6801 rows of the -08 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08) | ORB_THDL 0.344 = Air-Way 6801 rows of the -08 ORB size (A5; I3 = Brennan 6801 / 6801-L / 6801-LL STEPs at -08)</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>B(2) printed 7/8-14 with dims duplicating the 8-10 rows (an 8-8 takes 3/4-16; non-FG 8-8 prints it) - as-printed, likely scrambled row | HELD 2026-10-21 (group B): Air-Way prints this row with exactly the 6801-LL-08-10 values (M12 3.25, locknut 1.00, ORB bore 0.48; open question D 2026-10-18 "ignore it? recommended yes") - Brennan CAD record: M 1.25, M7 2.48, C 0.875, Y 0.75, B1D 0.391, B2D 0.391; BRENNAN_6801-LL-08-08-NWO-FG: ORB tip 2.480, JIC leg 1.250</t>
+          <t>B(2) printed 7/8-14 with dims duplicating the 8-10 rows (an 8-8 takes 3/4-16; non-FG 8-8 prints it) - as-printed, likely scrambled row | Air-Way prints this row with the 6801-LL-08-10 values (M 1.31, M12 3.25, C4HEX 1, Y 0.94, D1 0.39, D2 0.48) -&gt; every dimension cell = the Brennan CAD record (user 2026-10-21 "use brennan"; = BRENNAN_6801-LL-08-08-NWO-FG: ORB tip 2.480, JIC leg 1.250)</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
